--- a/services_forms/008_lawn_care_landscaping_new_client_questionnaire--services_forms.xlsx
+++ b/services_forms/008_lawn_care_landscaping_new_client_questionnaire--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -895,29 +895,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lawn_type</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lawn Type</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lawn_preferences_choices</t>
+          <t>lawn_condition_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lawn_type</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lawn Type</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dry</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dry</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -946,29 +946,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>damaged</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Damaged</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lawn_condition_choices</t>
+          <t>services_requests_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>damaged</t>
+          <t>aeration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Damaged</t>
+          <t>Aeration</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>aeration</t>
+          <t>mowing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aeration</t>
+          <t>Mowing</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mowing</t>
+          <t>trimming</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mowing</t>
+          <t>Trimming</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>trimming</t>
+          <t>pruning</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trimming</t>
+          <t>Pruning</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pruning</t>
+          <t>fertilization</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pruning</t>
+          <t>Fertilization</t>
         </is>
       </c>
     </row>
@@ -1048,29 +1048,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fertilization</t>
+          <t>weeding</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fertilization</t>
+          <t>Weeding</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>services_requests_choices</t>
+          <t>preferred_contact_method_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>weeding</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Weeding</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1099,27 +1099,10 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>preferred_contact_method_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>sms</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t>SMS</t>
         </is>
